--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6919-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6919-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2F6265D-6428-48DC-B2F1-9B8675319D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF96E82A-1F5D-4691-8C89-C922588814CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{04A9FCEC-D958-45B0-B304-DC1EF96A4DAC}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3632E752-60D6-4730-B282-266B55F1AEA7}"/>
   </bookViews>
   <sheets>
     <sheet name="6919-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1469,17 +1469,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6046E4-BE6A-426C-9BCD-DC9A08B363CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80650F30-99ED-4072-82DA-F57578B0C2B0}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="17" width="8.109375" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="17" width="10.125" customWidth="1"/>
+    <col min="18" max="18" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1537,7 +1537,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1633,7 +1633,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2024</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2023</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2022</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
         <v>42</v>
       </c>
